--- a/StructureDefinition-onc-fluid-balance.xlsx
+++ b/StructureDefinition-onc-fluid-balance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T01:44:04+00:00</t>
+    <t>2026-01-03T21:32:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-fluid-balance.xlsx
+++ b/StructureDefinition-onc-fluid-balance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T21:32:36+00:00</t>
+    <t>2026-01-26T10:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-fluid-balance.xlsx
+++ b/StructureDefinition-onc-fluid-balance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T10:54:48+00:00</t>
+    <t>2026-01-26T11:35:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-fluid-balance.xlsx
+++ b/StructureDefinition-onc-fluid-balance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T11:35:16+00:00</t>
+    <t>2026-01-26T23:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-fluid-balance.xlsx
+++ b/StructureDefinition-onc-fluid-balance.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T23:55:12+00:00</t>
+    <t>2026-01-27T00:24:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-fluid-balance.xlsx
+++ b/StructureDefinition-onc-fluid-balance.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://fhir.clinyq.ai/StructureDefinition/onc-fluid-balance</t>
+    <t>https://opennursingcoreig.com/StructureDefinition/onc-fluid-balance</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T00:24:44+00:00</t>
+    <t>2026-01-27T01:09:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-fluid-balance.xlsx
+++ b/StructureDefinition-onc-fluid-balance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T01:09:05+00:00</t>
+    <t>2026-01-27T08:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-fluid-balance.xlsx
+++ b/StructureDefinition-onc-fluid-balance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T08:26:02+00:00</t>
+    <t>2026-01-27T09:30:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-fluid-balance.xlsx
+++ b/StructureDefinition-onc-fluid-balance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T09:30:37+00:00</t>
+    <t>2026-06-29T21:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-fluid-balance.xlsx
+++ b/StructureDefinition-onc-fluid-balance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T21:13:26+00:00</t>
+    <t>2026-07-04T08:39:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-fluid-balance.xlsx
+++ b/StructureDefinition-onc-fluid-balance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T08:39:09+00:00</t>
+    <t>2026-07-04T09:17:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-fluid-balance.xlsx
+++ b/StructureDefinition-onc-fluid-balance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T09:17:49+00:00</t>
+    <t>2026-07-09T21:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-fluid-balance.xlsx
+++ b/StructureDefinition-onc-fluid-balance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T21:51:52+00:00</t>
+    <t>2026-07-09T22:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-fluid-balance.xlsx
+++ b/StructureDefinition-onc-fluid-balance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:02:23+00:00</t>
+    <t>2026-07-09T22:05:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-fluid-balance.xlsx
+++ b/StructureDefinition-onc-fluid-balance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:05:12+00:00</t>
+    <t>2026-07-09T22:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-fluid-balance.xlsx
+++ b/StructureDefinition-onc-fluid-balance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:28:17+00:00</t>
+    <t>2026-07-10T11:01:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-fluid-balance.xlsx
+++ b/StructureDefinition-onc-fluid-balance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T11:01:35+00:00</t>
+    <t>2026-07-11T09:35:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-fluid-balance.xlsx
+++ b/StructureDefinition-onc-fluid-balance.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4151" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4151" uniqueCount="560">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T09:35:24+00:00</t>
+    <t>2026-07-11T09:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -617,14 +617,6 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://terminology.hl7.org/CodeSystem/observation-category"/&gt;
-    &lt;code value="exam"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Codes for high level observation categories.</t>
@@ -3887,7 +3879,7 @@
         <v>18</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>193</v>
+        <v>18</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>18</v>
@@ -3905,23 +3897,23 @@
         <v>114</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB15" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>187</v>
@@ -3948,10 +3940,10 @@
         <v>18</v>
       </c>
       <c r="AN15" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>18</v>
@@ -3959,13 +3951,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>187</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>18</v>
@@ -4009,7 +4001,7 @@
         <v>18</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>18</v>
@@ -4027,10 +4019,10 @@
         <v>114</v>
       </c>
       <c r="Y16" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>18</v>
@@ -4072,10 +4064,10 @@
         <v>18</v>
       </c>
       <c r="AN16" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>18</v>
@@ -4083,14 +4075,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4112,16 +4104,16 @@
         <v>188</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>18</v>
@@ -4131,29 +4123,29 @@
         <v>18</v>
       </c>
       <c r="S17" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="T17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W17" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X17" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="T17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W17" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X17" t="s" s="2">
+      <c r="Y17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA17" t="s" s="2">
         <v>18</v>
       </c>
@@ -4170,7 +4162,7 @@
         <v>18</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>90</v>
@@ -4185,30 +4177,30 @@
         <v>102</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AL17" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AM17" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AO17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>218</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4231,19 +4223,19 @@
         <v>91</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>18</v>
@@ -4292,7 +4284,7 @@
         <v>18</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4307,19 +4299,19 @@
         <v>102</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>18</v>
@@ -4327,10 +4319,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4353,16 +4345,16 @@
         <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4412,7 +4404,7 @@
         <v>18</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4433,13 +4425,13 @@
         <v>18</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>18</v>
@@ -4447,14 +4439,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4473,19 +4465,19 @@
         <v>91</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>237</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="N20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>18</v>
@@ -4534,7 +4526,7 @@
         <v>18</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4549,19 +4541,19 @@
         <v>102</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>18</v>
@@ -4569,14 +4561,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4595,19 +4587,19 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>18</v>
@@ -4656,7 +4648,7 @@
         <v>18</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4671,19 +4663,19 @@
         <v>102</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AL21" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>256</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>18</v>
@@ -4691,10 +4683,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4717,16 +4709,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4776,7 +4768,7 @@
         <v>18</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4797,13 +4789,13 @@
         <v>18</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="AN22" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>18</v>
@@ -4811,10 +4803,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4837,17 +4829,17 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>18</v>
@@ -4896,7 +4888,7 @@
         <v>18</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4911,19 +4903,19 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>18</v>
@@ -4931,10 +4923,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4957,19 +4949,19 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>18</v>
@@ -5018,7 +5010,7 @@
         <v>18</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5027,7 +5019,7 @@
         <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>102</v>
@@ -5036,27 +5028,27 @@
         <v>18</v>
       </c>
       <c r="AL24" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP24" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5079,13 +5071,13 @@
         <v>18</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5136,7 +5128,7 @@
         <v>18</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5160,7 +5152,7 @@
         <v>18</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>18</v>
@@ -5171,10 +5163,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5203,7 +5195,7 @@
         <v>137</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N26" t="s" s="2">
         <v>139</v>
@@ -5244,19 +5236,19 @@
         <v>18</v>
       </c>
       <c r="AB26" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AC26" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AC26" t="s" s="2">
+      <c r="AD26" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AF26" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5280,7 +5272,7 @@
         <v>18</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>18</v>
@@ -5291,10 +5283,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5317,19 +5309,19 @@
         <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>18</v>
@@ -5378,7 +5370,7 @@
         <v>18</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5399,10 +5391,10 @@
         <v>18</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>18</v>
@@ -5413,10 +5405,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5442,20 +5434,20 @@
         <v>110</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="P28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q28" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="P28" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q28" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="R28" t="s" s="2">
         <v>18</v>
@@ -5479,28 +5471,28 @@
         <v>179</v>
       </c>
       <c r="Y28" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="Z28" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="Z28" t="s" s="2">
+      <c r="AA28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5521,10 +5513,10 @@
         <v>18</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>18</v>
@@ -5535,10 +5527,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5561,17 +5553,17 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>18</v>
@@ -5581,46 +5573,46 @@
         <v>18</v>
       </c>
       <c r="S29" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="T29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5641,10 +5633,10 @@
         <v>18</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>18</v>
@@ -5655,10 +5647,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5684,14 +5676,14 @@
         <v>104</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>18</v>
@@ -5701,46 +5693,46 @@
         <v>18</v>
       </c>
       <c r="S30" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="T30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5749,7 +5741,7 @@
         <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>102</v>
@@ -5761,10 +5753,10 @@
         <v>18</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>18</v>
@@ -5775,10 +5767,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5804,16 +5796,16 @@
         <v>110</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>18</v>
@@ -5823,7 +5815,7 @@
         <v>18</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>18</v>
@@ -5862,7 +5854,7 @@
         <v>18</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5883,10 +5875,10 @@
         <v>18</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>18</v>
@@ -5897,10 +5889,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5926,16 +5918,16 @@
         <v>188</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>18</v>
@@ -5960,14 +5952,14 @@
         <v>18</v>
       </c>
       <c r="X32" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="Y32" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="Y32" t="s" s="2">
+      <c r="Z32" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="Z32" t="s" s="2">
-        <v>345</v>
-      </c>
       <c r="AA32" t="s" s="2">
         <v>18</v>
       </c>
@@ -5984,7 +5976,7 @@
         <v>18</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5993,7 +5985,7 @@
         <v>90</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>102</v>
@@ -6008,7 +6000,7 @@
         <v>133</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>18</v>
@@ -6019,14 +6011,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -6048,16 +6040,16 @@
         <v>188</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>18</v>
@@ -6082,14 +6074,14 @@
         <v>18</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Y33" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="Z33" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="Z33" t="s" s="2">
-        <v>355</v>
-      </c>
       <c r="AA33" t="s" s="2">
         <v>18</v>
       </c>
@@ -6106,7 +6098,7 @@
         <v>18</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6124,27 +6116,27 @@
         <v>18</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP33" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>359</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6167,19 +6159,19 @@
         <v>18</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>18</v>
@@ -6228,7 +6220,7 @@
         <v>18</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6249,10 +6241,10 @@
         <v>18</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>18</v>
@@ -6263,10 +6255,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6292,13 +6284,13 @@
         <v>188</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6324,14 +6316,14 @@
         <v>18</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y35" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="Z35" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="Z35" t="s" s="2">
-        <v>373</v>
-      </c>
       <c r="AA35" t="s" s="2">
         <v>18</v>
       </c>
@@ -6348,7 +6340,7 @@
         <v>18</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6366,27 +6358,27 @@
         <v>18</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP35" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>377</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6412,16 +6404,16 @@
         <v>188</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>18</v>
@@ -6446,14 +6438,14 @@
         <v>18</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="Z36" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="Z36" t="s" s="2">
-        <v>384</v>
-      </c>
       <c r="AA36" t="s" s="2">
         <v>18</v>
       </c>
@@ -6470,7 +6462,7 @@
         <v>18</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6491,10 +6483,10 @@
         <v>18</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>18</v>
@@ -6505,10 +6497,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6531,16 +6523,16 @@
         <v>18</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6590,7 +6582,7 @@
         <v>18</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6608,27 +6600,27 @@
         <v>18</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>395</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6651,16 +6643,16 @@
         <v>18</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6710,7 +6702,7 @@
         <v>18</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6728,27 +6720,27 @@
         <v>18</v>
       </c>
       <c r="AL38" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP38" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>404</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6771,19 +6763,19 @@
         <v>18</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>18</v>
@@ -6832,7 +6824,7 @@
         <v>18</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6844,19 +6836,19 @@
         <v>18</v>
       </c>
       <c r="AJ39" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="AK39" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>18</v>
@@ -6867,10 +6859,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6893,13 +6885,13 @@
         <v>18</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6950,7 +6942,7 @@
         <v>18</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6974,7 +6966,7 @@
         <v>18</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>18</v>
@@ -6985,10 +6977,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7017,7 +7009,7 @@
         <v>137</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>139</v>
@@ -7070,7 +7062,7 @@
         <v>18</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7094,7 +7086,7 @@
         <v>18</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>18</v>
@@ -7105,14 +7097,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7134,10 +7126,10 @@
         <v>136</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>139</v>
@@ -7192,7 +7184,7 @@
         <v>18</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7227,10 +7219,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7253,13 +7245,13 @@
         <v>18</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7310,7 +7302,7 @@
         <v>18</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7319,7 +7311,7 @@
         <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>102</v>
@@ -7331,10 +7323,10 @@
         <v>18</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>18</v>
@@ -7345,10 +7337,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7371,13 +7363,13 @@
         <v>18</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7428,7 +7420,7 @@
         <v>18</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7437,7 +7429,7 @@
         <v>90</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>102</v>
@@ -7449,10 +7441,10 @@
         <v>18</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>18</v>
@@ -7463,10 +7455,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7492,16 +7484,16 @@
         <v>188</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>18</v>
@@ -7529,11 +7521,11 @@
         <v>114</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="Z45" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="Z45" t="s" s="2">
-        <v>438</v>
-      </c>
       <c r="AA45" t="s" s="2">
         <v>18</v>
       </c>
@@ -7550,7 +7542,7 @@
         <v>18</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7568,13 +7560,13 @@
         <v>18</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AM45" t="s" s="2">
-        <v>440</v>
-      </c>
       <c r="AN45" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>18</v>
@@ -7585,10 +7577,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7614,16 +7606,16 @@
         <v>188</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>18</v>
@@ -7648,14 +7640,14 @@
         <v>18</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Y46" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="Z46" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="Z46" t="s" s="2">
-        <v>447</v>
-      </c>
       <c r="AA46" t="s" s="2">
         <v>18</v>
       </c>
@@ -7672,7 +7664,7 @@
         <v>18</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7690,13 +7682,13 @@
         <v>18</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="AM46" t="s" s="2">
-        <v>440</v>
-      </c>
       <c r="AN46" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>18</v>
@@ -7707,10 +7699,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7733,17 +7725,17 @@
         <v>18</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>18</v>
@@ -7792,7 +7784,7 @@
         <v>18</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7816,7 +7808,7 @@
         <v>18</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>18</v>
@@ -7827,10 +7819,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7853,13 +7845,13 @@
         <v>18</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7910,7 +7902,7 @@
         <v>18</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7931,10 +7923,10 @@
         <v>18</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>18</v>
@@ -7945,10 +7937,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7971,16 +7963,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8030,7 +8022,7 @@
         <v>18</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8051,10 +8043,10 @@
         <v>18</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>18</v>
@@ -8065,10 +8057,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8091,16 +8083,16 @@
         <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8150,7 +8142,7 @@
         <v>18</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8171,10 +8163,10 @@
         <v>18</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>18</v>
@@ -8185,10 +8177,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8211,19 +8203,19 @@
         <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>18</v>
@@ -8260,17 +8252,17 @@
         <v>18</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AC51" s="2"/>
       <c r="AD51" t="s" s="2">
         <v>18</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8291,10 +8283,10 @@
         <v>18</v>
       </c>
       <c r="AM51" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>18</v>
@@ -8305,10 +8297,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8331,13 +8323,13 @@
         <v>18</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8388,7 +8380,7 @@
         <v>18</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8412,7 +8404,7 @@
         <v>18</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>18</v>
@@ -8423,10 +8415,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8455,7 +8447,7 @@
         <v>137</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>139</v>
@@ -8508,7 +8500,7 @@
         <v>18</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8532,7 +8524,7 @@
         <v>18</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>18</v>
@@ -8543,14 +8535,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8572,10 +8564,10 @@
         <v>136</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>139</v>
@@ -8630,7 +8622,7 @@
         <v>18</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8665,10 +8657,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8694,16 +8686,16 @@
         <v>188</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="N55" t="s" s="2">
-        <v>485</v>
-      </c>
       <c r="O55" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>18</v>
@@ -8728,14 +8720,14 @@
         <v>18</v>
       </c>
       <c r="X55" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y55" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y55" t="s" s="2">
+      <c r="Z55" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>18</v>
       </c>
@@ -8752,7 +8744,7 @@
         <v>18</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>90</v>
@@ -8770,16 +8762,16 @@
         <v>18</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AM55" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN55" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>18</v>
@@ -8787,10 +8779,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8813,19 +8805,19 @@
         <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="M56" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>490</v>
-      </c>
       <c r="O56" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>18</v>
@@ -8874,7 +8866,7 @@
         <v>18</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8892,27 +8884,27 @@
         <v>18</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AM56" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP56" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8938,16 +8930,16 @@
         <v>188</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="N57" t="s" s="2">
-        <v>495</v>
-      </c>
       <c r="O57" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>18</v>
@@ -8972,14 +8964,14 @@
         <v>18</v>
       </c>
       <c r="X57" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="Y57" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="Y57" t="s" s="2">
+      <c r="Z57" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="Z57" t="s" s="2">
-        <v>345</v>
-      </c>
       <c r="AA57" t="s" s="2">
         <v>18</v>
       </c>
@@ -8996,7 +8988,7 @@
         <v>18</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9005,7 +8997,7 @@
         <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>102</v>
@@ -9020,7 +9012,7 @@
         <v>133</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>18</v>
@@ -9031,14 +9023,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9060,16 +9052,16 @@
         <v>188</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>18</v>
@@ -9094,14 +9086,14 @@
         <v>18</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="Z58" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>355</v>
-      </c>
       <c r="AA58" t="s" s="2">
         <v>18</v>
       </c>
@@ -9118,7 +9110,7 @@
         <v>18</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9136,27 +9128,27 @@
         <v>18</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>359</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9182,16 +9174,16 @@
         <v>80</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>499</v>
-      </c>
       <c r="N59" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="O59" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>18</v>
@@ -9240,7 +9232,7 @@
         <v>18</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9261,10 +9253,10 @@
         <v>18</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>18</v>
@@ -9275,13 +9267,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C60" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="C60" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>18</v>
@@ -9303,19 +9295,19 @@
         <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>18</v>
@@ -9364,7 +9356,7 @@
         <v>18</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9385,10 +9377,10 @@
         <v>18</v>
       </c>
       <c r="AM60" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>18</v>
@@ -9399,10 +9391,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9425,13 +9417,13 @@
         <v>18</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9482,7 +9474,7 @@
         <v>18</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9506,7 +9498,7 @@
         <v>18</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>18</v>
@@ -9517,10 +9509,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9549,7 +9541,7 @@
         <v>137</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>139</v>
@@ -9602,7 +9594,7 @@
         <v>18</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9626,7 +9618,7 @@
         <v>18</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>18</v>
@@ -9637,14 +9629,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9666,10 +9658,10 @@
         <v>136</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>139</v>
@@ -9724,7 +9716,7 @@
         <v>18</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9759,10 +9751,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9788,16 +9780,16 @@
         <v>188</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="N64" t="s" s="2">
-        <v>485</v>
-      </c>
       <c r="O64" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>18</v>
@@ -9807,7 +9799,7 @@
         <v>18</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>18</v>
@@ -9822,14 +9814,14 @@
         <v>18</v>
       </c>
       <c r="X64" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y64" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y64" t="s" s="2">
+      <c r="Z64" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z64" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA64" t="s" s="2">
         <v>18</v>
       </c>
@@ -9846,7 +9838,7 @@
         <v>18</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>90</v>
@@ -9864,16 +9856,16 @@
         <v>18</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AM64" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>18</v>
@@ -9881,10 +9873,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9907,19 +9899,19 @@
         <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="M65" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>490</v>
-      </c>
       <c r="O65" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>18</v>
@@ -9968,7 +9960,7 @@
         <v>18</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9986,27 +9978,27 @@
         <v>18</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AM65" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN65" t="s" s="2">
+      <c r="AO65" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP65" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="B66" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10029,13 +10021,13 @@
         <v>18</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10086,7 +10078,7 @@
         <v>18</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10110,7 +10102,7 @@
         <v>18</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>18</v>
@@ -10121,10 +10113,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="B67" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10153,7 +10145,7 @@
         <v>137</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>139</v>
@@ -10194,19 +10186,19 @@
         <v>18</v>
       </c>
       <c r="AB67" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AC67" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AC67" t="s" s="2">
+      <c r="AD67" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AF67" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10230,7 +10222,7 @@
         <v>18</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>18</v>
@@ -10241,10 +10233,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10267,19 +10259,19 @@
         <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>18</v>
@@ -10328,7 +10320,7 @@
         <v>18</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10349,10 +10341,10 @@
         <v>18</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>18</v>
@@ -10363,10 +10355,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B69" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10392,20 +10384,20 @@
         <v>110</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q69" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="P69" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q69" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="R69" t="s" s="2">
         <v>18</v>
@@ -10429,28 +10421,28 @@
         <v>179</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="Z69" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="Z69" t="s" s="2">
+      <c r="AA69" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10471,10 +10463,10 @@
         <v>18</v>
       </c>
       <c r="AM69" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>18</v>
@@ -10485,10 +10477,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="B70" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10511,17 +10503,17 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>18</v>
@@ -10531,46 +10523,46 @@
         <v>18</v>
       </c>
       <c r="S70" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10591,10 +10583,10 @@
         <v>18</v>
       </c>
       <c r="AM70" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>18</v>
@@ -10605,10 +10597,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="B71" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10634,14 +10626,14 @@
         <v>104</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>18</v>
@@ -10651,46 +10643,46 @@
         <v>18</v>
       </c>
       <c r="S71" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10699,7 +10691,7 @@
         <v>90</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>102</v>
@@ -10711,10 +10703,10 @@
         <v>18</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>18</v>
@@ -10725,10 +10717,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="B72" t="s" s="2">
         <v>520</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>521</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10754,16 +10746,16 @@
         <v>110</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="N72" t="s" s="2">
+      <c r="O72" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>18</v>
@@ -10773,7 +10765,7 @@
         <v>18</v>
       </c>
       <c r="S72" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="T72" t="s" s="2">
         <v>18</v>
@@ -10812,7 +10804,7 @@
         <v>18</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10833,10 +10825,10 @@
         <v>18</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>18</v>
@@ -10847,10 +10839,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10876,16 +10868,16 @@
         <v>188</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="N73" t="s" s="2">
-        <v>495</v>
-      </c>
       <c r="O73" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>18</v>
@@ -10910,14 +10902,14 @@
         <v>18</v>
       </c>
       <c r="X73" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="Y73" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="Y73" t="s" s="2">
+      <c r="Z73" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="Z73" t="s" s="2">
-        <v>345</v>
-      </c>
       <c r="AA73" t="s" s="2">
         <v>18</v>
       </c>
@@ -10934,7 +10926,7 @@
         <v>18</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10943,7 +10935,7 @@
         <v>90</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>102</v>
@@ -10958,7 +10950,7 @@
         <v>133</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>18</v>
@@ -10969,14 +10961,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10998,16 +10990,16 @@
         <v>188</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>18</v>
@@ -11032,14 +11024,14 @@
         <v>18</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Y74" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="Z74" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="Z74" t="s" s="2">
-        <v>355</v>
-      </c>
       <c r="AA74" t="s" s="2">
         <v>18</v>
       </c>
@@ -11056,7 +11048,7 @@
         <v>18</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11074,27 +11066,27 @@
         <v>18</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AN74" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AN74" t="s" s="2">
+      <c r="AO74" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>359</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11120,16 +11112,16 @@
         <v>80</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M75" t="s" s="2">
-        <v>499</v>
-      </c>
       <c r="N75" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="O75" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>18</v>
@@ -11178,7 +11170,7 @@
         <v>18</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11199,10 +11191,10 @@
         <v>18</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>18</v>
@@ -11213,13 +11205,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C76" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="C76" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>18</v>
@@ -11241,19 +11233,19 @@
         <v>91</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="N76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>18</v>
@@ -11302,7 +11294,7 @@
         <v>18</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11323,10 +11315,10 @@
         <v>18</v>
       </c>
       <c r="AM76" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>18</v>
@@ -11337,10 +11329,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11363,13 +11355,13 @@
         <v>18</v>
       </c>
       <c r="K77" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11420,7 +11412,7 @@
         <v>18</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11444,7 +11436,7 @@
         <v>18</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>18</v>
@@ -11455,10 +11447,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11487,7 +11479,7 @@
         <v>137</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>139</v>
@@ -11540,7 +11532,7 @@
         <v>18</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11564,7 +11556,7 @@
         <v>18</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>18</v>
@@ -11575,14 +11567,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11604,10 +11596,10 @@
         <v>136</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>139</v>
@@ -11662,7 +11654,7 @@
         <v>18</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11697,10 +11689,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11726,16 +11718,16 @@
         <v>188</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="N80" t="s" s="2">
-        <v>485</v>
-      </c>
       <c r="O80" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>18</v>
@@ -11745,7 +11737,7 @@
         <v>18</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>18</v>
@@ -11760,14 +11752,14 @@
         <v>18</v>
       </c>
       <c r="X80" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y80" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y80" t="s" s="2">
+      <c r="Z80" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z80" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA80" t="s" s="2">
         <v>18</v>
       </c>
@@ -11784,7 +11776,7 @@
         <v>18</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>90</v>
@@ -11802,16 +11794,16 @@
         <v>18</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AM80" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN80" t="s" s="2">
+      <c r="AO80" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>18</v>
@@ -11819,10 +11811,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11845,19 +11837,19 @@
         <v>91</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N81" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="M81" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>490</v>
-      </c>
       <c r="O81" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>18</v>
@@ -11906,7 +11898,7 @@
         <v>18</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11924,27 +11916,27 @@
         <v>18</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AM81" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN81" t="s" s="2">
+      <c r="AO81" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP81" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP81" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11967,13 +11959,13 @@
         <v>18</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12024,7 +12016,7 @@
         <v>18</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -12048,7 +12040,7 @@
         <v>18</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>18</v>
@@ -12059,10 +12051,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12091,7 +12083,7 @@
         <v>137</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>139</v>
@@ -12132,19 +12124,19 @@
         <v>18</v>
       </c>
       <c r="AB83" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AC83" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AC83" t="s" s="2">
+      <c r="AD83" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AF83" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12168,7 +12160,7 @@
         <v>18</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>18</v>
@@ -12179,10 +12171,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12205,19 +12197,19 @@
         <v>91</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="N84" t="s" s="2">
+      <c r="O84" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>18</v>
@@ -12266,7 +12258,7 @@
         <v>18</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12287,10 +12279,10 @@
         <v>18</v>
       </c>
       <c r="AM84" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>18</v>
@@ -12301,10 +12293,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12330,20 +12322,20 @@
         <v>110</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="P85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q85" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="P85" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q85" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="R85" t="s" s="2">
         <v>18</v>
@@ -12367,28 +12359,28 @@
         <v>179</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="Z85" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="Z85" t="s" s="2">
+      <c r="AA85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12409,10 +12401,10 @@
         <v>18</v>
       </c>
       <c r="AM85" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>18</v>
@@ -12423,10 +12415,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12449,17 +12441,17 @@
         <v>91</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>18</v>
@@ -12469,46 +12461,46 @@
         <v>18</v>
       </c>
       <c r="S86" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF86" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="T86" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12529,10 +12521,10 @@
         <v>18</v>
       </c>
       <c r="AM86" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>18</v>
@@ -12543,10 +12535,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12572,14 +12564,14 @@
         <v>104</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>18</v>
@@ -12589,46 +12581,46 @@
         <v>18</v>
       </c>
       <c r="S87" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF87" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="T87" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12637,7 +12629,7 @@
         <v>90</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>102</v>
@@ -12649,10 +12641,10 @@
         <v>18</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>18</v>
@@ -12663,10 +12655,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12692,16 +12684,16 @@
         <v>110</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M88" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>18</v>
@@ -12711,7 +12703,7 @@
         <v>18</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>18</v>
@@ -12750,7 +12742,7 @@
         <v>18</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12771,10 +12763,10 @@
         <v>18</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>18</v>
@@ -12785,10 +12777,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12814,16 +12806,16 @@
         <v>188</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="N89" t="s" s="2">
-        <v>495</v>
-      </c>
       <c r="O89" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>18</v>
@@ -12848,14 +12840,14 @@
         <v>18</v>
       </c>
       <c r="X89" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="Y89" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="Y89" t="s" s="2">
+      <c r="Z89" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="Z89" t="s" s="2">
-        <v>345</v>
-      </c>
       <c r="AA89" t="s" s="2">
         <v>18</v>
       </c>
@@ -12872,7 +12864,7 @@
         <v>18</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12881,7 +12873,7 @@
         <v>90</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>102</v>
@@ -12896,7 +12888,7 @@
         <v>133</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>18</v>
@@ -12907,14 +12899,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -12936,16 +12928,16 @@
         <v>188</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="N90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>18</v>
@@ -12970,14 +12962,14 @@
         <v>18</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Y90" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="Z90" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="Z90" t="s" s="2">
-        <v>355</v>
-      </c>
       <c r="AA90" t="s" s="2">
         <v>18</v>
       </c>
@@ -12994,7 +12986,7 @@
         <v>18</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13012,27 +13004,27 @@
         <v>18</v>
       </c>
       <c r="AL90" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AM90" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AM90" t="s" s="2">
+      <c r="AN90" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AN90" t="s" s="2">
+      <c r="AO90" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP90" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP90" t="s" s="2">
-        <v>359</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13058,16 +13050,16 @@
         <v>80</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M91" t="s" s="2">
-        <v>499</v>
-      </c>
       <c r="N91" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="O91" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>18</v>
@@ -13116,7 +13108,7 @@
         <v>18</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13137,10 +13129,10 @@
         <v>18</v>
       </c>
       <c r="AM91" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>18</v>
@@ -13151,13 +13143,13 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C92" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="C92" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="D92" t="s" s="2">
         <v>18</v>
@@ -13179,19 +13171,19 @@
         <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="N92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>18</v>
@@ -13240,7 +13232,7 @@
         <v>18</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13261,10 +13253,10 @@
         <v>18</v>
       </c>
       <c r="AM92" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AN92" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>18</v>
@@ -13275,10 +13267,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13301,13 +13293,13 @@
         <v>18</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13358,7 +13350,7 @@
         <v>18</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13382,7 +13374,7 @@
         <v>18</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>18</v>
@@ -13393,10 +13385,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13425,7 +13417,7 @@
         <v>137</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>139</v>
@@ -13478,7 +13470,7 @@
         <v>18</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13502,7 +13494,7 @@
         <v>18</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>18</v>
@@ -13513,14 +13505,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13542,10 +13534,10 @@
         <v>136</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N95" t="s" s="2">
         <v>139</v>
@@ -13600,7 +13592,7 @@
         <v>18</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13635,10 +13627,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13664,16 +13656,16 @@
         <v>188</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="N96" t="s" s="2">
-        <v>485</v>
-      </c>
       <c r="O96" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>18</v>
@@ -13683,7 +13675,7 @@
         <v>18</v>
       </c>
       <c r="S96" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="T96" t="s" s="2">
         <v>18</v>
@@ -13698,14 +13690,14 @@
         <v>18</v>
       </c>
       <c r="X96" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="Y96" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="Y96" t="s" s="2">
+      <c r="Z96" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="Z96" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="AA96" t="s" s="2">
         <v>18</v>
       </c>
@@ -13722,7 +13714,7 @@
         <v>18</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>90</v>
@@ -13740,16 +13732,16 @@
         <v>18</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AM96" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AN96" t="s" s="2">
+      <c r="AO96" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>18</v>
@@ -13757,10 +13749,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13783,19 +13775,19 @@
         <v>91</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L97" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="M97" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>490</v>
-      </c>
       <c r="O97" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>18</v>
@@ -13844,7 +13836,7 @@
         <v>18</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13862,27 +13854,27 @@
         <v>18</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AM97" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN97" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AN97" t="s" s="2">
+      <c r="AO97" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP97" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13905,13 +13897,13 @@
         <v>18</v>
       </c>
       <c r="K98" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="L98" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L98" t="s" s="2">
+      <c r="M98" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13962,7 +13954,7 @@
         <v>18</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13986,7 +13978,7 @@
         <v>18</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>18</v>
@@ -13997,10 +13989,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14029,7 +14021,7 @@
         <v>137</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>139</v>
@@ -14070,19 +14062,19 @@
         <v>18</v>
       </c>
       <c r="AB99" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AC99" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AC99" t="s" s="2">
+      <c r="AD99" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AF99" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14106,7 +14098,7 @@
         <v>18</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>18</v>
@@ -14117,10 +14109,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14143,19 +14135,19 @@
         <v>91</v>
       </c>
       <c r="K100" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L100" t="s" s="2">
         <v>297</v>
       </c>
-      <c r="L100" t="s" s="2">
+      <c r="M100" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="N100" t="s" s="2">
+      <c r="O100" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>18</v>
@@ -14204,7 +14196,7 @@
         <v>18</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14225,10 +14217,10 @@
         <v>18</v>
       </c>
       <c r="AM100" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AN100" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>18</v>
@@ -14239,10 +14231,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14268,20 +14260,20 @@
         <v>110</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="P101" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Q101" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="P101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Q101" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="R101" t="s" s="2">
         <v>18</v>
@@ -14305,28 +14297,28 @@
         <v>179</v>
       </c>
       <c r="Y101" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="Z101" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="Z101" t="s" s="2">
+      <c r="AA101" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF101" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14347,10 +14339,10 @@
         <v>18</v>
       </c>
       <c r="AM101" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AN101" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>18</v>
@@ -14361,10 +14353,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14387,17 +14379,17 @@
         <v>91</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>317</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>18</v>
@@ -14407,46 +14399,46 @@
         <v>18</v>
       </c>
       <c r="S102" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF102" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="T102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14467,10 +14459,10 @@
         <v>18</v>
       </c>
       <c r="AM102" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AN102" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>18</v>
@@ -14481,10 +14473,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14510,14 +14502,14 @@
         <v>104</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>18</v>
@@ -14527,46 +14519,46 @@
         <v>18</v>
       </c>
       <c r="S103" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AF103" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="T103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14575,7 +14567,7 @@
         <v>90</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>102</v>
@@ -14587,10 +14579,10 @@
         <v>18</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>18</v>
@@ -14601,10 +14593,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14630,16 +14622,16 @@
         <v>110</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M104" t="s" s="2">
+      <c r="N104" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="N104" t="s" s="2">
+      <c r="O104" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>18</v>
@@ -14649,7 +14641,7 @@
         <v>18</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>18</v>
@@ -14688,7 +14680,7 @@
         <v>18</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14709,10 +14701,10 @@
         <v>18</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>18</v>
@@ -14723,10 +14715,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14752,16 +14744,16 @@
         <v>188</v>
       </c>
       <c r="L105" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M105" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M105" t="s" s="2">
+      <c r="N105" t="s" s="2">
         <v>494</v>
       </c>
-      <c r="N105" t="s" s="2">
-        <v>495</v>
-      </c>
       <c r="O105" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>18</v>
@@ -14786,14 +14778,14 @@
         <v>18</v>
       </c>
       <c r="X105" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="Y105" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="Y105" t="s" s="2">
+      <c r="Z105" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="Z105" t="s" s="2">
-        <v>345</v>
-      </c>
       <c r="AA105" t="s" s="2">
         <v>18</v>
       </c>
@@ -14810,7 +14802,7 @@
         <v>18</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14819,7 +14811,7 @@
         <v>90</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>102</v>
@@ -14834,7 +14826,7 @@
         <v>133</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>18</v>
@@ -14845,14 +14837,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -14874,16 +14866,16 @@
         <v>188</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="N106" t="s" s="2">
+      <c r="O106" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>18</v>
@@ -14908,14 +14900,14 @@
         <v>18</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Y106" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="Z106" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="Z106" t="s" s="2">
-        <v>355</v>
-      </c>
       <c r="AA106" t="s" s="2">
         <v>18</v>
       </c>
@@ -14932,7 +14924,7 @@
         <v>18</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -14950,27 +14942,27 @@
         <v>18</v>
       </c>
       <c r="AL106" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AM106" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AM106" t="s" s="2">
+      <c r="AN106" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="AN106" t="s" s="2">
+      <c r="AO106" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="AP106" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="AP106" t="s" s="2">
-        <v>359</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14996,16 +14988,16 @@
         <v>80</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="M107" t="s" s="2">
-        <v>499</v>
-      </c>
       <c r="N107" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="O107" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="O107" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>18</v>
@@ -15054,7 +15046,7 @@
         <v>18</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -15075,10 +15067,10 @@
         <v>18</v>
       </c>
       <c r="AM107" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AN107" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>18</v>

--- a/StructureDefinition-onc-fluid-balance.xlsx
+++ b/StructureDefinition-onc-fluid-balance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T09:46:48+00:00</t>
+    <t>2026-07-11T14:02:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-fluid-balance.xlsx
+++ b/StructureDefinition-onc-fluid-balance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:02:42+00:00</t>
+    <t>2026-07-11T14:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-fluid-balance.xlsx
+++ b/StructureDefinition-onc-fluid-balance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:17:07+00:00</t>
+    <t>2026-07-11T14:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-fluid-balance.xlsx
+++ b/StructureDefinition-onc-fluid-balance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:32:04+00:00</t>
+    <t>2026-07-11T14:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-fluid-balance.xlsx
+++ b/StructureDefinition-onc-fluid-balance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:47:20+00:00</t>
+    <t>2026-07-11T18:02:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
